--- a/frontend/templates/用例集导入模板.xlsx
+++ b/frontend/templates/用例集导入模板.xlsx
@@ -420,38 +420,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="23.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1">
+        <v>基线数量</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1">
+    <dataValidation type="whole" errorStyle="stop" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="基线数量无效" error="请输入不小于 1 的正整数，或留空。" sqref="C2:C1048576" allowBlank="1">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
